--- a/Models/Свиньи/results/Свиньи - Результаты прогнозов SARIMA.xlsx
+++ b/Models/Свиньи/results/Свиньи - Результаты прогнозов SARIMA.xlsx
@@ -488,41 +488,41 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>268.55</v>
+        <v>73.08</v>
       </c>
       <c r="G2" t="n">
-        <v>264.64</v>
+        <v>61.25</v>
       </c>
       <c r="H2" t="n">
-        <v>61.98</v>
+        <v>11.18</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[606.14, 765.78, 825.33]</t>
+          <t>[436.41, 525.28, 522.1]</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>[314.19, 565.5, 523.64]</t>
+          <t>[553.23, 566.96, 496.85]</t>
         </is>
       </c>
     </row>
@@ -534,17 +534,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -553,22 +553,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>118.53</v>
+        <v>154.51</v>
       </c>
       <c r="G3" t="n">
-        <v>104.44</v>
+        <v>110.54</v>
       </c>
       <c r="H3" t="n">
-        <v>19.72</v>
+        <v>22.52</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[502.57, 707.31, 581.87]</t>
+          <t>[569.74, 567.61, 746.67]</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>[565.5, 523.64, 515.15]</t>
+          <t>[566.96, 496.85, 488.59]</t>
         </is>
       </c>
     </row>
@@ -580,17 +580,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -599,22 +599,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>194.04</v>
+        <v>427.94</v>
       </c>
       <c r="G4" t="n">
-        <v>177.87</v>
+        <v>339.58</v>
       </c>
       <c r="H4" t="n">
-        <v>41.44</v>
+        <v>70.26000000000001</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[801.02, 603.33, 477.97]</t>
+          <t>[567.02, 745.43, 1171.78]</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>[523.64, 515.15, 309.94]</t>
+          <t>[496.85, 488.59, 480.05]</t>
         </is>
       </c>
     </row>
@@ -626,17 +626,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -645,22 +645,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>252.7</v>
+        <v>390.28</v>
       </c>
       <c r="G5" t="n">
-        <v>181.48</v>
+        <v>297.82</v>
       </c>
       <c r="H5" t="n">
-        <v>28.9</v>
+        <v>63.53</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[480.7, 391.25, 1226.04]</t>
+          <t>[714.92, 1116.26, 294.65]</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>[515.15, 309.94, 797.36]</t>
+          <t>[488.59, 480.05, 263.72]</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>(2, 0, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -691,22 +691,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>343.19</v>
+        <v>285.98</v>
       </c>
       <c r="G6" t="n">
-        <v>290.93</v>
+        <v>168.29</v>
       </c>
       <c r="H6" t="n">
-        <v>41.58</v>
+        <v>35.52</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>[410.85, 1333.73, 1180.78]</t>
+          <t>[975.33, 257.0, 343.66]</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>[309.94, 797.36, 945.29]</t>
+          <t>[480.05, 263.72, 340.79]</t>
         </is>
       </c>
     </row>
@@ -718,17 +718,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(1, 1, 2)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -737,22 +737,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>175.62</v>
+        <v>123.79</v>
       </c>
       <c r="G7" t="n">
-        <v>122.82</v>
+        <v>115.19</v>
       </c>
       <c r="H7" t="n">
-        <v>16.72</v>
+        <v>32.16</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>[1092.98, 946.45, 481.54]</t>
+          <t>[175.32, 262.62, 268.26]</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>[797.36, 945.29, 553.23]</t>
+          <t>[263.72, 340.79, 447.27]</t>
         </is>
       </c>
     </row>
@@ -764,41 +764,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 1, 2)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>117.89</v>
+        <v>124.06</v>
       </c>
       <c r="G8" t="n">
-        <v>113.4</v>
+        <v>103.02</v>
       </c>
       <c r="H8" t="n">
-        <v>17.2</v>
+        <v>22.74</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>[817.39, 409.67, 498.21]</t>
+          <t>[352.99, 330.1, 287.73]</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>[945.29, 553.23, 566.96]</t>
+          <t>[340.79, 447.27, 467.44]</t>
         </is>
       </c>
     </row>
@@ -810,41 +810,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(2, 1, 3)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>73.08</v>
+        <v>168.27</v>
       </c>
       <c r="G9" t="n">
-        <v>61.25</v>
+        <v>165.06</v>
       </c>
       <c r="H9" t="n">
-        <v>11.18</v>
+        <v>41.01</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>[436.41, 525.28, 522.1]</t>
+          <t>[302.65, 256.26, 166.75]</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>[553.23, 566.96, 496.85]</t>
+          <t>[447.27, 467.44, 306.14]</t>
         </is>
       </c>
     </row>
@@ -856,41 +856,41 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 1, 1)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>154.51</v>
+        <v>101.7</v>
       </c>
       <c r="G10" t="n">
-        <v>110.54</v>
+        <v>91</v>
       </c>
       <c r="H10" t="n">
-        <v>22.52</v>
+        <v>21.61</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>[569.74, 567.61, 746.67]</t>
+          <t>[316.93, 223.99, 653.88]</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>[566.96, 496.85, 488.59]</t>
+          <t>[467.44, 306.14, 694.22]</t>
         </is>
       </c>
     </row>
@@ -902,41 +902,41 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 1, 5)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>427.94</v>
+        <v>145.69</v>
       </c>
       <c r="G11" t="n">
-        <v>339.58</v>
+        <v>123.8</v>
       </c>
       <c r="H11" t="n">
-        <v>70.26000000000001</v>
+        <v>21.79</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>[567.02, 745.43, 1171.78]</t>
+          <t>[216.39, 642.74, 573.6]</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>[496.85, 488.59, 480.05]</t>
+          <t>[306.14, 694.22, 803.75]</t>
         </is>
       </c>
     </row>
@@ -948,12 +948,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -967,22 +967,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>67</v>
+        <v>9.5</v>
       </c>
       <c r="G12" t="n">
-        <v>61.98</v>
+        <v>7.39</v>
       </c>
       <c r="H12" t="n">
-        <v>71.79000000000001</v>
+        <v>12.15</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>[17.03, 19.11, 35.24]</t>
+          <t>[7.14, 49.97, 65.7]</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>[60.6, 63.5, 133.2]</t>
+          <t>[7.6, 56.7, 80.7]</t>
         </is>
       </c>
     </row>
@@ -994,12 +994,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1013,22 +1013,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>49.7</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>47.05</v>
+        <v>6.22</v>
       </c>
       <c r="H13" t="n">
-        <v>47.03</v>
+        <v>9.1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>[37.16, 67.82, 48.39]</t>
+          <t>[51.54, 67.75, 24.95]</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>[63.5, 133.2, 97.8]</t>
+          <t>[56.7, 80.7, 25.5]</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1059,22 +1059,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>32.9</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>27.38</v>
+        <v>7.23</v>
       </c>
       <c r="H14" t="n">
-        <v>29.78</v>
+        <v>23.39</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>[88.19, 62.92, 9.13]</t>
+          <t>[71.17, 26.19, 32.06]</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>[133.2, 97.8, 11.4]</t>
+          <t>[80.7, 25.5, 20.6]</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1105,22 +1105,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>16</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>13.13</v>
+        <v>7.05</v>
       </c>
       <c r="H15" t="n">
-        <v>12.55</v>
+        <v>27.84</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>[77.61, 11.17, 107.93]</t>
+          <t>[27.89, 34.06, 55.0]</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>[97.8, 11.4, 126.9]</t>
+          <t>[25.5, 20.6, 60.3]</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1151,22 +1151,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.98</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>3.55</v>
+        <v>7.73</v>
       </c>
       <c r="H16" t="n">
-        <v>8.02</v>
+        <v>25.55</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>[12.52, 121.49, 37.38]</t>
+          <t>[32.54, 52.56, 56.2]</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>[11.4, 126.9, 41.5]</t>
+          <t>[20.6, 60.3, 59.7]</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1197,22 +1197,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>7.08</v>
+        <v>26.48</v>
       </c>
       <c r="G17" t="n">
-        <v>5.88</v>
+        <v>23.95</v>
       </c>
       <c r="H17" t="n">
-        <v>12.38</v>
+        <v>27.88</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>[116.14, 35.73, 6.48]</t>
+          <t>[42.51, 45.44, 91.71]</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>[126.9, 41.5, 7.6]</t>
+          <t>[60.3, 59.7, 131.5]</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1243,22 +1243,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5.9</v>
+        <v>16.05</v>
       </c>
       <c r="G18" t="n">
-        <v>4.75</v>
+        <v>14.53</v>
       </c>
       <c r="H18" t="n">
-        <v>12.4</v>
+        <v>14.12</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>[37.37, 6.78, 47.38]</t>
+          <t>[54.6, 110.42, 80.49]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>[41.5, 7.6, 56.7]</t>
+          <t>[59.7, 131.5, 97.9]</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1289,22 +1289,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>9.5</v>
+        <v>12.08</v>
       </c>
       <c r="G19" t="n">
-        <v>7.39</v>
+        <v>10.17</v>
       </c>
       <c r="H19" t="n">
-        <v>12.15</v>
+        <v>12.47</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>[7.14, 49.97, 65.7]</t>
+          <t>[115.64, 84.29, 10.25]</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>[7.6, 56.7, 80.7]</t>
+          <t>[131.5, 97.9, 9.2]</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1335,22 +1335,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>8.050000000000001</v>
+        <v>6.74</v>
       </c>
       <c r="G20" t="n">
-        <v>6.22</v>
+        <v>6.02</v>
       </c>
       <c r="H20" t="n">
-        <v>9.1</v>
+        <v>11.21</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>[51.54, 67.75, 24.95]</t>
+          <t>[90.06, 10.95, 119.02]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>[56.7, 80.7, 25.5]</t>
+          <t>[97.9, 9.2, 127.5]</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1381,22 +1381,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>8.619999999999999</v>
+        <v>2.39</v>
       </c>
       <c r="G21" t="n">
-        <v>7.23</v>
+        <v>2.23</v>
       </c>
       <c r="H21" t="n">
-        <v>23.39</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>[71.17, 26.19, 32.06]</t>
+          <t>[11.42, 124.22, 39.91]</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>[80.7, 25.5, 20.6]</t>
+          <t>[9.2, 127.5, 41.1]</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1427,22 +1427,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>80.37</v>
+        <v>144.24</v>
       </c>
       <c r="G22" t="n">
-        <v>60.53</v>
+        <v>135.34</v>
       </c>
       <c r="H22" t="n">
-        <v>83.81</v>
+        <v>40.04</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>[119.98, 171.43, 202.91]</t>
+          <t>[148.17, 262.29, 177.46]</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>[68.43, 172.15, 73.6]</t>
+          <t>[236.84, 466.77, 290.34]</t>
         </is>
       </c>
     </row>
@@ -1454,17 +1454,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1473,22 +1473,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>81.53</v>
+        <v>130.16</v>
       </c>
       <c r="G23" t="n">
-        <v>69.16</v>
+        <v>118.45</v>
       </c>
       <c r="H23" t="n">
-        <v>77.01000000000001</v>
+        <v>302.77</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>[162.89, 182.95, 204.16]</t>
+          <t>[272.23, 204.88, 84.35]</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>[172.15, 73.6, 115.3]</t>
+          <t>[466.77, 290.34, 9.0]</t>
         </is>
       </c>
     </row>
@@ -1500,17 +1500,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1519,22 +1519,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>112.32</v>
+        <v>57.6</v>
       </c>
       <c r="G24" t="n">
-        <v>111.02</v>
+        <v>50</v>
       </c>
       <c r="H24" t="n">
-        <v>118.16</v>
+        <v>319.22</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>[185.22, 205.12, 236.97]</t>
+          <t>[237.97, 92.77, 142.35]</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>[73.6, 115.3, 105.35]</t>
+          <t>[290.34, 9.0, 156.2]</t>
         </is>
       </c>
     </row>
@@ -1546,41 +1546,41 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>(0, 0, 5)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>(2, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>65.41</v>
+        <v>52.44</v>
       </c>
       <c r="G25" t="n">
-        <v>59.3</v>
+        <v>36.57</v>
       </c>
       <c r="H25" t="n">
-        <v>56.65</v>
+        <v>341.54</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>[148.46, 152.61, 198.68]</t>
+          <t>[98.64, 148.67, 65.24]</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>[115.3, 105.35, 101.19]</t>
+          <t>[9.0, 156.2, 52.7]</t>
         </is>
       </c>
     </row>
@@ -1592,41 +1592,41 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>89.36</v>
+        <v>40.52</v>
       </c>
       <c r="G26" t="n">
-        <v>85.62</v>
+        <v>35.61</v>
       </c>
       <c r="H26" t="n">
-        <v>83.45999999999999</v>
+        <v>33.45</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>[186.56, 220.08, 158.49]</t>
+          <t>[93.55, 34.06, 77.14]</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>[105.35, 101.19, 101.72]</t>
+          <t>[156.2, 52.7, 102.7]</t>
         </is>
       </c>
     </row>
@@ -1638,41 +1638,41 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>(1, 1, 2, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>69.04000000000001</v>
+        <v>75</v>
       </c>
       <c r="G27" t="n">
-        <v>63.32</v>
+        <v>53.4</v>
       </c>
       <c r="H27" t="n">
-        <v>46.63</v>
+        <v>40.06</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>[182.4, 126.18, 152.54]</t>
+          <t>[37.83, 85.23, 42.74]</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>[101.19, 101.72, 236.84]</t>
+          <t>[52.7, 102.7, 170.6]</t>
         </is>
       </c>
     </row>
@@ -1684,41 +1684,41 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>124.47</v>
+        <v>74.84</v>
       </c>
       <c r="G28" t="n">
-        <v>97.59999999999999</v>
+        <v>56.54</v>
       </c>
       <c r="H28" t="n">
-        <v>29.36</v>
+        <v>58.86</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>[111.69, 151.9, 268.86]</t>
+          <t>[90.31, 45.69, 67.71]</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>[101.72, 236.84, 466.77]</t>
+          <t>[102.7, 170.6, 35.4]</t>
         </is>
       </c>
     </row>
@@ -1730,41 +1730,41 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>144.24</v>
+        <v>81.06</v>
       </c>
       <c r="G29" t="n">
-        <v>135.34</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>40.04</v>
+        <v>216.32</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>[148.17, 262.29, 177.46]</t>
+          <t>[46.7, 69.24, 68.53]</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>[236.84, 466.77, 290.34]</t>
+          <t>[170.6, 35.4, 11.8]</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1791,26 +1791,26 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>130.16</v>
+        <v>70.95</v>
       </c>
       <c r="G30" t="n">
-        <v>118.45</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>302.77</v>
+        <v>360.32</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>[272.23, 204.88, 84.35]</t>
+          <t>[99.93, 100.78, 92.96]</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>[466.77, 290.34, 9.0]</t>
+          <t>[35.4, 11.8, 38.0]</t>
         </is>
       </c>
     </row>
@@ -1822,41 +1822,41 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>57.6</v>
+        <v>46.17</v>
       </c>
       <c r="G31" t="n">
-        <v>50</v>
+        <v>44.2</v>
       </c>
       <c r="H31" t="n">
-        <v>319.22</v>
+        <v>252.18</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>[237.97, 92.77, 142.35]</t>
+          <t>[74.38, 69.41, 65.51]</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>[290.34, 9.0, 156.2]</t>
+          <t>[11.8, 38.0, 26.9]</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(1, 0, 3)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1887,13 +1887,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3.73</v>
+        <v>2.19</v>
       </c>
       <c r="G32" t="n">
-        <v>2.38</v>
+        <v>1.27</v>
       </c>
       <c r="H32" t="n">
-        <v>2.29024587477129e+18</v>
+        <v>2.942174175566317e+20</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>[0.71, 6.43, 0.0]</t>
+          <t>[3.8, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -1914,17 +1914,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>(3, 0, 3)</t>
+          <t>(1, 0, 3)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1933,22 +1933,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>2.716658251615153e+19</v>
+        <v>7.541947021488435e+20</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>[0.01, 0.0, 0.0]</t>
+          <t>[0.0, 0.01, 0.0]</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>[6.43, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -1960,12 +1960,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2.082723534362527e+20</v>
+        <v>3.661116376312199e+20</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2031,7 +2031,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.595767533960913e+19</v>
+        <v>1.871254545747375e+19</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2052,12 +2052,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2077,11 +2077,11 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.337045467880301e+19</v>
+        <v>5.77631914614957e+19</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2098,12 +2098,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>5.50740100819126e+16</v>
+        <v>5.804521597987439e+19</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 3.8]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2144,12 +2144,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2163,22 +2163,22 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>3.913344043487066e+19</v>
+        <v>1.049160041290956e+19</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
+          <t>[0.0, -0.0, -0.0]</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
           <t>[0.0, 0.0, 0.0]</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>[0.0, 3.8, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2190,12 +2190,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2209,22 +2209,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>2.942174175566317e+20</v>
+        <v>2.068730997815509e+17</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
+          <t>[-0.0, -0.0, -0.0]</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
           <t>[0.0, 0.0, 0.0]</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>[3.8, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2261,11 +2261,11 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>7.541947021488435e+20</v>
+        <v>2.2042918226489e+17</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>[0.0, 0.01, 0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2282,17 +2282,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(1, 0, 3)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2307,11 +2307,11 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>3.661116376312199e+20</v>
+        <v>1.871001118341105e+17</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2328,17 +2328,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>(1, 1, 2)</t>
+          <t>(0, 1, 2)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2347,22 +2347,22 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>118.21</v>
+        <v>107.83</v>
       </c>
       <c r="G42" t="n">
-        <v>116.15</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>32.21</v>
+        <v>20.88</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>[234.66, 211.59, 282.04]</t>
+          <t>[305.14, 300.31, 293.26]</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>[325.4, 324.95, 426.38]</t>
+          <t>[463.17, 399.19, 304.73]</t>
         </is>
       </c>
     </row>
@@ -2374,12 +2374,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2393,22 +2393,22 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>121.77</v>
+        <v>157.15</v>
       </c>
       <c r="G43" t="n">
-        <v>121.47</v>
+        <v>136.81</v>
       </c>
       <c r="H43" t="n">
-        <v>31.64</v>
+        <v>43.7</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>[215.22, 301.28, 277.76]</t>
+          <t>[429.28, 474.25, 521.23]</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>[324.95, 426.38, 407.34]</t>
+          <t>[399.19, 304.73, 310.4]</t>
         </is>
       </c>
     </row>
@@ -2420,17 +2420,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(1, 1, 2)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2439,22 +2439,22 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>73.02</v>
+        <v>308.97</v>
       </c>
       <c r="G44" t="n">
-        <v>72.94</v>
+        <v>276.15</v>
       </c>
       <c r="H44" t="n">
-        <v>18.18</v>
+        <v>69.3</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>[353.08, 330.41, 303.02]</t>
+          <t>[465.94, 506.56, 984.3]</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>[426.38, 407.34, 371.6]</t>
+          <t>[304.73, 310.4, 513.21]</t>
         </is>
       </c>
     </row>
@@ -2466,17 +2466,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(1, 1, 2)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2485,22 +2485,22 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>98.64</v>
+        <v>171.96</v>
       </c>
       <c r="G45" t="n">
-        <v>84.28</v>
+        <v>162.97</v>
       </c>
       <c r="H45" t="n">
-        <v>16.69</v>
+        <v>40.8</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>[350.12, 332.03, 458.87]</t>
+          <t>[410.57, 747.04, 502.6]</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>[407.34, 371.6, 614.91]</t>
+          <t>[310.4, 513.21, 347.69]</t>
         </is>
       </c>
     </row>
@@ -2512,17 +2512,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(1, 1, 2)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2531,22 +2531,22 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>81.31</v>
+        <v>122.18</v>
       </c>
       <c r="G46" t="n">
-        <v>71.34</v>
+        <v>118.78</v>
       </c>
       <c r="H46" t="n">
-        <v>15.03</v>
+        <v>32.3</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>[348.89, 496.68, 296.66]</t>
+          <t>[657.82, 426.55, 421.51]</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>[371.6, 614.91, 369.74]</t>
+          <t>[513.21, 347.69, 288.64]</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2577,22 +2577,22 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>134.41</v>
+        <v>111.89</v>
       </c>
       <c r="G47" t="n">
-        <v>122.78</v>
+        <v>84.5</v>
       </c>
       <c r="H47" t="n">
-        <v>25.73</v>
+        <v>30.31</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>[505.63, 306.15, 267.69]</t>
+          <t>[357.38, 348.33, 457.06]</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>[614.91, 369.74, 463.17]</t>
+          <t>[347.69, 288.64, 272.95]</t>
         </is>
       </c>
     </row>
@@ -2604,12 +2604,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2623,22 +2623,22 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>122.34</v>
+        <v>140.2</v>
       </c>
       <c r="G48" t="n">
-        <v>111.98</v>
+        <v>129.93</v>
       </c>
       <c r="H48" t="n">
-        <v>26.43</v>
+        <v>47.1</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>[321.33, 294.72, 280.11]</t>
+          <t>[345.19, 450.56, 430.44]</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>[369.74, 463.17, 399.19]</t>
+          <t>[288.64, 272.95, 274.81]</t>
         </is>
       </c>
     </row>
@@ -2650,12 +2650,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2669,22 +2669,22 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>107.83</v>
+        <v>117.71</v>
       </c>
       <c r="G49" t="n">
-        <v>89.45999999999999</v>
+        <v>112.82</v>
       </c>
       <c r="H49" t="n">
-        <v>20.88</v>
+        <v>40.82</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>[305.14, 300.31, 293.26]</t>
+          <t>[424.88, 391.39, 357.05]</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>[463.17, 399.19, 304.73]</t>
+          <t>[272.95, 274.81, 287.1]</t>
         </is>
       </c>
     </row>
@@ -2696,41 +2696,41 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>(1, 1, 2)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>157.15</v>
+        <v>64.19</v>
       </c>
       <c r="G50" t="n">
-        <v>136.81</v>
+        <v>52.75</v>
       </c>
       <c r="H50" t="n">
-        <v>43.7</v>
+        <v>16.09</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>[429.28, 474.25, 521.23]</t>
+          <t>[324.74, 296.56, 467.55]</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>[399.19, 304.73, 310.4]</t>
+          <t>[274.81, 287.1, 368.67]</t>
         </is>
       </c>
     </row>
@@ -2742,41 +2742,41 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>(1, 1, 2)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>308.97</v>
+        <v>37.35</v>
       </c>
       <c r="G51" t="n">
-        <v>276.15</v>
+        <v>28.71</v>
       </c>
       <c r="H51" t="n">
-        <v>69.3</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>[465.94, 506.56, 984.3]</t>
+          <t>[273.42, 431.1, 258.93]</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>[304.73, 310.4, 513.21]</t>
+          <t>[287.1, 368.67, 268.94]</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2813,11 +2813,11 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>3.043797285539383e+18</v>
+        <v>4.567734404083365e+17</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2834,12 +2834,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2849,26 +2849,26 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="H53" t="n">
-        <v>2.23685571506997e+19</v>
+        <v>7.008120671890586e+16</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, 0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 1.4]</t>
         </is>
       </c>
     </row>
@@ -2880,12 +2880,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2899,22 +2899,22 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="H54" t="n">
-        <v>2.889070037441955e+20</v>
+        <v>6.355598657138829e+16</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, -0.0, 0.0]</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 1.4, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2926,12 +2926,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2941,26 +2941,26 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(2, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="H55" t="n">
-        <v>2.499516263470673e+20</v>
+        <v>6.37586559362453e+16</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[1.4, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2972,12 +2972,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2997,7 +2997,7 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>8.379942917731629e+19</v>
+        <v>3.139014273692034e+18</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3018,12 +3018,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -3043,7 +3043,7 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>5.096351955868013e+18</v>
+        <v>6.164709054245917e+17</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3064,12 +3064,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -3089,11 +3089,11 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>4.088784037301466e+17</v>
+        <v>2.183861475187536e+18</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, -0.0]</t>
+          <t>[-0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3110,12 +3110,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -3135,11 +3135,11 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>4.567734404083365e+17</v>
+        <v>1.631743857388851e+19</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3175,22 +3175,22 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>7.008120671890586e+16</v>
+        <v>1.700796409828943e+19</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 1.4]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -3202,12 +3202,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3221,22 +3221,22 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.27</v>
       </c>
       <c r="G61" t="n">
-        <v>0.47</v>
+        <v>0.73</v>
       </c>
       <c r="H61" t="n">
-        <v>6.355598657138829e+16</v>
+        <v>7.618774406113752e+18</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, 0.0]</t>
+          <t>[0.0, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>[0.0, 1.4, 0.0]</t>
+          <t>[0.0, 0.0, 2.2]</t>
         </is>
       </c>
     </row>
@@ -3248,12 +3248,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3267,22 +3267,22 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="G62" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="H62" t="n">
-        <v>1.825434045250373e+21</v>
+        <v>1.024456948722554e+17</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>[0.02, 0.0, 0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.1, 0.0]</t>
         </is>
       </c>
     </row>
@@ -3294,12 +3294,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3313,13 +3313,13 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="H63" t="n">
-        <v>1.645856731477657e+17</v>
+        <v>1.179281675157877e+17</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.1, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -3340,12 +3340,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3359,22 +3359,22 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H64" t="n">
-        <v>1.634356378149777e+17</v>
+        <v>1.085415089694758e+21</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, -0.0]</t>
+          <t>[0.01, 0.0, 0.29]</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.1]</t>
         </is>
       </c>
     </row>
@@ -3386,12 +3386,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3405,22 +3405,22 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="H65" t="n">
-        <v>1.62299515689303e+17</v>
+        <v>1.028066696955159e+17</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, -0.0]</t>
+          <t>[-0.0, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.1, 0.0]</t>
         </is>
       </c>
     </row>
@@ -3432,12 +3432,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3451,22 +3451,22 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="H66" t="n">
-        <v>1.611777093785621e+17</v>
+        <v>1.178814611615884e+17</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, -0.0]</t>
+          <t>[0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.1, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3503,11 +3503,11 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>1.600702706371767e+17</v>
+        <v>1.648474778925725e+18</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3543,13 +3543,13 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>9.547991277723536e+16</v>
+        <v>1.467769145676841e+17</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.1]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3589,13 +3589,13 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>1.024456948722554e+17</v>
+        <v>1.458576245330565e+17</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>[0.0, 0.1, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -3616,12 +3616,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3635,13 +3635,13 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>1.179281675157877e+17</v>
+        <v>1.449489293625985e+17</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>[0.1, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -3662,12 +3662,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3681,22 +3681,22 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>1.085415089694758e+21</v>
+        <v>1.440506837604918e+17</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>[0.01, 0.0, 0.29]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.1]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3727,22 +3727,22 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>0.4</v>
+        <v>0.61</v>
       </c>
       <c r="G72" t="n">
-        <v>0.39</v>
+        <v>0.49</v>
       </c>
       <c r="H72" t="n">
-        <v>15.2</v>
+        <v>10.34</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>[3.67, 3.38, 2.51]</t>
+          <t>[1.04, 5.07, 9.81]</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>[3.3, 3.1, 2.0]</t>
+          <t>[0.9, 5.4, 10.8]</t>
         </is>
       </c>
     </row>
@@ -3754,12 +3754,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3773,22 +3773,22 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>0.21</v>
+        <v>1.18</v>
       </c>
       <c r="G73" t="n">
-        <v>0.16</v>
+        <v>1.09</v>
       </c>
       <c r="H73" t="n">
-        <v>7.41</v>
+        <v>14.17</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>[3.18, 2.36, 2.26]</t>
+          <t>[4.69, 9.09, 5.45]</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>[3.1, 2.0, 2.3]</t>
+          <t>[5.4, 10.8, 6.3]</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3819,22 +3819,22 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>0.19</v>
+        <v>1.21</v>
       </c>
       <c r="G74" t="n">
-        <v>0.14</v>
+        <v>1.06</v>
       </c>
       <c r="H74" t="n">
-        <v>7.43</v>
+        <v>8.07</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>[2.33, 2.23, 1.13]</t>
+          <t>[9.84, 5.9, 18.37]</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>[2.0, 2.3, 1.1]</t>
+          <t>[10.8, 6.3, 20.2]</t>
         </is>
       </c>
     </row>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3865,22 +3865,22 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="G75" t="n">
-        <v>0.11</v>
+        <v>0.33</v>
       </c>
       <c r="H75" t="n">
-        <v>6.18</v>
+        <v>2.24</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>[2.05, 1.04, 1.47]</t>
+          <t>[6.21, 19.34, 3.34]</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>[2.3, 1.1, 1.5]</t>
+          <t>[6.3, 20.2, 3.3]</t>
         </is>
       </c>
     </row>
@@ -3892,12 +3892,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3911,22 +3911,22 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>0.06</v>
+        <v>0.42</v>
       </c>
       <c r="G76" t="n">
-        <v>0.05</v>
+        <v>0.27</v>
       </c>
       <c r="H76" t="n">
-        <v>3.52</v>
+        <v>2.2</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>[1.11, 1.56, 1.38]</t>
+          <t>[19.48, 3.36, 3.14]</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>[1.1, 1.5, 1.3]</t>
+          <t>[20.2, 3.3, 3.1]</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3957,22 +3957,22 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>0.12</v>
+        <v>0.85</v>
       </c>
       <c r="G77" t="n">
-        <v>0.1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H77" t="n">
-        <v>9.710000000000001</v>
+        <v>71.88</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>[1.55, 1.37, 1.08]</t>
+          <t>[3.43, 3.2, 2.16]</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>[1.5, 1.3, 0.9]</t>
+          <t>[3.3, 3.1, 0.7]</t>
         </is>
       </c>
     </row>
@@ -3984,12 +3984,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4003,22 +4003,22 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>0.17</v>
+        <v>1.11</v>
       </c>
       <c r="G78" t="n">
-        <v>0.15</v>
+        <v>0.91</v>
       </c>
       <c r="H78" t="n">
-        <v>8.59</v>
+        <v>110.74</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>[1.35, 1.06, 5.17]</t>
+          <t>[3.13, 2.12, 2.29]</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>[1.3, 0.9, 5.4]</t>
+          <t>[3.1, 0.7, 1.0]</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4049,22 +4049,22 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>0.61</v>
+        <v>1.1</v>
       </c>
       <c r="G79" t="n">
-        <v>0.49</v>
+        <v>0.9</v>
       </c>
       <c r="H79" t="n">
-        <v>10.34</v>
+        <v>109.73</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>[1.04, 5.07, 9.81]</t>
+          <t>[2.1, 2.28, 1.11]</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>[0.9, 5.4, 10.8]</t>
+          <t>[0.7, 1.0, 1.1]</t>
         </is>
       </c>
     </row>
@@ -4076,12 +4076,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4095,22 +4095,22 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1.18</v>
+        <v>0.32</v>
       </c>
       <c r="G80" t="n">
-        <v>1.09</v>
+        <v>0.27</v>
       </c>
       <c r="H80" t="n">
-        <v>14.17</v>
+        <v>25.47</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>[4.69, 9.09, 5.45]</t>
+          <t>[1.26, 0.61, 0.85]</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>[5.4, 10.8, 6.3]</t>
+          <t>[1.0, 1.1, 0.9]</t>
         </is>
       </c>
     </row>
@@ -4122,12 +4122,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4141,22 +4141,22 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1.21</v>
+        <v>0.35</v>
       </c>
       <c r="G81" t="n">
-        <v>1.06</v>
+        <v>0.29</v>
       </c>
       <c r="H81" t="n">
-        <v>8.07</v>
+        <v>29.68</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>[9.84, 5.9, 18.37]</t>
+          <t>[0.53, 0.74, 0.64]</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>[10.8, 6.3, 20.2]</t>
+          <t>[1.1, 0.9, 0.8]</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4187,22 +4187,22 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>7.02</v>
+        <v>7.54</v>
       </c>
       <c r="G82" t="n">
-        <v>6.33</v>
+        <v>6.79</v>
       </c>
       <c r="H82" t="n">
-        <v>17.48</v>
+        <v>30.3</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>[37.99, 23.8, 27.48]</t>
+          <t>[20.06, 47.87, 38.49]</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>[48.0, 30.2, 24.9]</t>
+          <t>[13.9, 51.0, 27.4]</t>
         </is>
       </c>
     </row>
@@ -4214,12 +4214,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4233,22 +4233,22 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>4.25</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="G83" t="n">
-        <v>3.48</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="H83" t="n">
-        <v>13.09</v>
+        <v>17.96</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>[26.87, 31.44, 29.98]</t>
+          <t>[40.56, 31.47, 42.36]</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>[30.2, 24.9, 29.4]</t>
+          <t>[51.0, 27.4, 52.0]</t>
         </is>
       </c>
     </row>
@@ -4260,12 +4260,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4279,22 +4279,22 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>5.89</v>
+        <v>5.05</v>
       </c>
       <c r="G84" t="n">
-        <v>5.37</v>
+        <v>4.3</v>
       </c>
       <c r="H84" t="n">
-        <v>26.98</v>
+        <v>13.41</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>[33.36, 31.99, 18.37]</t>
+          <t>[35.07, 47.96, 25.7]</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>[24.9, 29.4, 13.3]</t>
+          <t>[27.4, 52.0, 26.9]</t>
         </is>
       </c>
     </row>
@@ -4306,12 +4306,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4325,22 +4325,22 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>14.51</v>
+        <v>10.89</v>
       </c>
       <c r="G85" t="n">
-        <v>9.67</v>
+        <v>9.81</v>
       </c>
       <c r="H85" t="n">
-        <v>18.15</v>
+        <v>22.26</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>[27.66, 15.6, 54.93]</t>
+          <t>[42.69, 22.6, 32.27]</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>[29.4, 13.3, 79.9]</t>
+          <t>[52.0, 26.9, 48.1]</t>
         </is>
       </c>
     </row>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4371,22 +4371,22 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>13.5</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G86" t="n">
-        <v>8.85</v>
+        <v>7.69</v>
       </c>
       <c r="H86" t="n">
-        <v>17.63</v>
+        <v>20.69</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>[16.09, 56.69, 19.54]</t>
+          <t>[24.9, 35.88, 21.45]</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>[13.3, 79.9, 19.0]</t>
+          <t>[26.9, 48.1, 30.3]</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4417,22 +4417,22 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>16.25</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="G87" t="n">
-        <v>10.93</v>
+        <v>7.63</v>
       </c>
       <c r="H87" t="n">
-        <v>22.44</v>
+        <v>21.69</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>[52.0, 17.55, 17.34]</t>
+          <t>[37.26, 22.35, 21.01]</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>[79.9, 19.0, 13.9]</t>
+          <t>[48.1, 30.3, 25.1]</t>
         </is>
       </c>
     </row>
@@ -4444,12 +4444,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4463,22 +4463,22 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>4.43</v>
+        <v>4.06</v>
       </c>
       <c r="G88" t="n">
-        <v>3.28</v>
+        <v>3.61</v>
       </c>
       <c r="H88" t="n">
-        <v>21.68</v>
+        <v>12.27</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>[21.23, 21.24, 50.74]</t>
+          <t>[25.32, 24.08, 24.85]</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>[19.0, 13.9, 51.0]</t>
+          <t>[30.3, 25.1, 29.7]</t>
         </is>
       </c>
     </row>
@@ -4490,12 +4490,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4509,22 +4509,22 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>7.54</v>
+        <v>1.52</v>
       </c>
       <c r="G89" t="n">
-        <v>6.79</v>
+        <v>1.24</v>
       </c>
       <c r="H89" t="n">
-        <v>30.3</v>
+        <v>4.69</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>[20.06, 47.87, 38.49]</t>
+          <t>[26.3, 27.37, 13.11]</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>[13.9, 51.0, 27.4]</t>
+          <t>[25.1, 29.7, 13.3]</t>
         </is>
       </c>
     </row>
@@ -4536,12 +4536,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4555,22 +4555,22 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>8.539999999999999</v>
+        <v>13.7</v>
       </c>
       <c r="G90" t="n">
-        <v>8.050000000000001</v>
+        <v>9</v>
       </c>
       <c r="H90" t="n">
-        <v>17.96</v>
+        <v>14.06</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>[40.56, 31.47, 42.36]</t>
+          <t>[26.75, 12.78, 59.66]</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>[51.0, 27.4, 52.0]</t>
+          <t>[29.7, 13.3, 83.2]</t>
         </is>
       </c>
     </row>
@@ -4582,12 +4582,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4601,22 +4601,22 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>5.05</v>
+        <v>13.34</v>
       </c>
       <c r="G91" t="n">
-        <v>4.3</v>
+        <v>10.56</v>
       </c>
       <c r="H91" t="n">
-        <v>13.41</v>
+        <v>84.84</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>[35.07, 47.96, 25.7]</t>
+          <t>[13.45, 63.14, 16.46]</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>[27.4, 52.0, 26.9]</t>
+          <t>[13.3, 83.2, 5.0]</t>
         </is>
       </c>
     </row>
@@ -4628,17 +4628,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>(5, 0, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4647,22 +4647,22 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>31.57</v>
+        <v>29.84</v>
       </c>
       <c r="G92" t="n">
-        <v>28.28</v>
+        <v>26.15</v>
       </c>
       <c r="H92" t="n">
-        <v>15.24</v>
+        <v>15.19</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>[114.46, 162.22, 188.79]</t>
+          <t>[160.15, 141.27, 132.24]</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>[143.6, 172.9, 233.8]</t>
+          <t>[167.7, 169.6, 174.8]</t>
         </is>
       </c>
     </row>
@@ -4674,41 +4674,41 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>(2, 0, 2)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>27.76</v>
+        <v>32.52</v>
       </c>
       <c r="G93" t="n">
-        <v>25.21</v>
+        <v>31.81</v>
       </c>
       <c r="H93" t="n">
-        <v>12.23</v>
+        <v>18.98</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>[153.59, 192.35, 205.66]</t>
+          <t>[142.73, 133.43, 128.72]</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>[172.9, 233.8, 190.8]</t>
+          <t>[169.6, 174.8, 155.9]</t>
         </is>
       </c>
     </row>
@@ -4720,12 +4720,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4735,26 +4735,26 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>(1, 1, 2, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>21.78</v>
+        <v>31.17</v>
       </c>
       <c r="G94" t="n">
-        <v>18.8</v>
+        <v>30.65</v>
       </c>
       <c r="H94" t="n">
-        <v>8.26</v>
+        <v>18.28</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>[201.15, 185.03, 213.31]</t>
+          <t>[138.67, 133.01, 201.84]</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>[233.8, 190.8, 231.3]</t>
+          <t>[174.8, 155.9, 168.9]</t>
         </is>
       </c>
     </row>
@@ -4766,12 +4766,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4785,22 +4785,22 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>22.88</v>
+        <v>29.72</v>
       </c>
       <c r="G95" t="n">
-        <v>16.79</v>
+        <v>23.94</v>
       </c>
       <c r="H95" t="n">
-        <v>10.82</v>
+        <v>14.94</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>[199.47, 228.13, 183.67]</t>
+          <t>[145.67, 217.69, 149.4]</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>[190.8, 231.3, 145.13]</t>
+          <t>[155.9, 168.9, 136.6]</t>
         </is>
       </c>
     </row>
@@ -4812,12 +4812,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4827,26 +4827,26 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>22.46</v>
+        <v>25.93</v>
       </c>
       <c r="G96" t="n">
-        <v>17.76</v>
+        <v>20.04</v>
       </c>
       <c r="H96" t="n">
-        <v>11.46</v>
+        <v>12.22</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>[225.65, 182.12, 154.65]</t>
+          <t>[212.2, 128.98, 177.81]</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>[231.3, 145.13, 165.3]</t>
+          <t>[168.9, 136.6, 168.6]</t>
         </is>
       </c>
     </row>
@@ -4858,12 +4858,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4873,26 +4873,26 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>22.86</v>
+        <v>11.37</v>
       </c>
       <c r="G97" t="n">
-        <v>17.56</v>
+        <v>9.31</v>
       </c>
       <c r="H97" t="n">
-        <v>11.67</v>
+        <v>5.25</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>[183.17, 155.4, 162.98]</t>
+          <t>[124.38, 168.32, 217.36]</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>[145.13, 165.3, 167.7]</t>
+          <t>[136.6, 168.6, 232.8]</t>
         </is>
       </c>
     </row>
@@ -4904,12 +4904,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4919,26 +4919,26 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>22.08</v>
+        <v>20.46</v>
       </c>
       <c r="G98" t="n">
-        <v>20.48</v>
+        <v>16.05</v>
       </c>
       <c r="H98" t="n">
-        <v>12.19</v>
+        <v>7.49</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>[147.13, 155.98, 138.05]</t>
+          <t>[171.7, 221.05, 180.51]</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>[165.3, 167.7, 169.6]</t>
+          <t>[168.6, 232.8, 213.8]</t>
         </is>
       </c>
     </row>
@@ -4950,12 +4950,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4965,26 +4965,26 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>29.84</v>
+        <v>21.76</v>
       </c>
       <c r="G99" t="n">
-        <v>26.15</v>
+        <v>19.11</v>
       </c>
       <c r="H99" t="n">
-        <v>15.19</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>[160.15, 141.27, 132.24]</t>
+          <t>[220.12, 180.01, 212.55]</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>[167.7, 169.6, 174.8]</t>
+          <t>[232.8, 213.8, 223.4]</t>
         </is>
       </c>
     </row>
@@ -4996,12 +4996,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5011,26 +5011,26 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>32.52</v>
+        <v>21.5</v>
       </c>
       <c r="G100" t="n">
-        <v>31.81</v>
+        <v>19.34</v>
       </c>
       <c r="H100" t="n">
-        <v>18.98</v>
+        <v>9.49</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>[142.73, 133.43, 128.72]</t>
+          <t>[182.05, 214.35, 162.88]</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>[169.6, 174.8, 155.9]</t>
+          <t>[213.8, 223.4, 180.1]</t>
         </is>
       </c>
     </row>
@@ -5042,12 +5042,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5057,26 +5057,26 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>31.17</v>
+        <v>6.29</v>
       </c>
       <c r="G101" t="n">
-        <v>30.65</v>
+        <v>4.93</v>
       </c>
       <c r="H101" t="n">
-        <v>18.28</v>
+        <v>2.75</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>[138.67, 133.01, 201.84]</t>
+          <t>[222.26, 169.8, 163.25]</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>[174.8, 155.9, 168.9]</t>
+          <t>[223.4, 180.1, 166.6]</t>
         </is>
       </c>
     </row>
@@ -5088,17 +5088,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -5107,22 +5107,22 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>81.56999999999999</v>
+        <v>150.25</v>
       </c>
       <c r="G102" t="n">
-        <v>69.45999999999999</v>
+        <v>141.81</v>
       </c>
       <c r="H102" t="n">
-        <v>9.619999999999999</v>
+        <v>18.45</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>[571.96, 644.36, 750.11]</t>
+          <t>[845.87, 898.74, 987.5]</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>[627.0, 771.9, 724.31]</t>
+          <t>[731.19, 799.44, 776.04]</t>
         </is>
       </c>
     </row>
@@ -5134,17 +5134,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5153,22 +5153,22 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>70.73</v>
+        <v>110.12</v>
       </c>
       <c r="G103" t="n">
-        <v>65.97</v>
+        <v>79.86</v>
       </c>
       <c r="H103" t="n">
-        <v>8.59</v>
+        <v>10.17</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>[671.71, 763.27, 732.98]</t>
+          <t>[835.5, 962.55, 854.68]</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>[771.9, 724.31, 791.73]</t>
+          <t>[799.44, 776.04, 871.68]</t>
         </is>
       </c>
     </row>
@@ -5180,17 +5180,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>(1, 1, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -5199,22 +5199,22 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>69.38</v>
+        <v>199.96</v>
       </c>
       <c r="G104" t="n">
-        <v>57.56</v>
+        <v>165</v>
       </c>
       <c r="H104" t="n">
-        <v>7.69</v>
+        <v>18.93</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>[836.07, 768.2, 837.26]</t>
+          <t>[942.61, 845.8, 1237.22]</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>[724.31, 791.73, 799.86]</t>
+          <t>[776.04, 871.68, 934.66]</t>
         </is>
       </c>
     </row>
@@ -5226,17 +5226,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(1, 0, 2)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>48.09</v>
+        <v>141.62</v>
       </c>
       <c r="G105" t="n">
-        <v>37.76</v>
+        <v>119.4</v>
       </c>
       <c r="H105" t="n">
-        <v>4.75</v>
+        <v>13.53</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>[712.91, 809.02, 779.06]</t>
+          <t>[746.01, 1144.05, 591.53]</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>[791.73, 799.86, 804.37]</t>
+          <t>[871.68, 934.66, 614.67]</t>
         </is>
       </c>
     </row>
@@ -5272,17 +5272,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5291,22 +5291,22 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>91.53</v>
+        <v>191.39</v>
       </c>
       <c r="G106" t="n">
-        <v>69.45</v>
+        <v>138.47</v>
       </c>
       <c r="H106" t="n">
-        <v>9.140000000000001</v>
+        <v>16.32</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>[850.08, 796.41, 595.37]</t>
+          <t>[1256.21, 629.21, 729.34]</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>[799.86, 804.37, 745.53]</t>
+          <t>[934.66, 614.67, 650.04]</t>
         </is>
       </c>
     </row>
@@ -5318,17 +5318,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>(1, 1, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -5337,22 +5337,22 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>93.83</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="G107" t="n">
-        <v>70.02</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="H107" t="n">
-        <v>9.359999999999999</v>
+        <v>9.57</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>[784.7, 587.49, 698.84]</t>
+          <t>[544.26, 682.83, 771.87]</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>[804.37, 745.53, 731.19]</t>
+          <t>[614.67, 650.04, 879.3]</t>
         </is>
       </c>
     </row>
@@ -5364,12 +5364,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5383,22 +5383,22 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>77.09999999999999</v>
+        <v>162.93</v>
       </c>
       <c r="G108" t="n">
-        <v>70.89</v>
+        <v>138.44</v>
       </c>
       <c r="H108" t="n">
-        <v>9.369999999999999</v>
+        <v>15.06</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>[632.78, 773.08, 857.45]</t>
+          <t>[719.76, 793.29, 792.65]</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>[745.53, 731.19, 799.44]</t>
+          <t>[650.04, 879.3, 1052.23]</t>
         </is>
       </c>
     </row>
@@ -5410,12 +5410,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>150.25</v>
+        <v>259.38</v>
       </c>
       <c r="G109" t="n">
-        <v>141.81</v>
+        <v>243.39</v>
       </c>
       <c r="H109" t="n">
-        <v>18.45</v>
+        <v>22.73</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>[845.87, 898.74, 987.5]</t>
+          <t>[757.93, 777.65, 847.56]</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>[731.19, 799.44, 776.04]</t>
+          <t>[879.3, 1052.23, 1181.78]</t>
         </is>
       </c>
     </row>
@@ -5456,12 +5456,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5475,22 +5475,22 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>110.12</v>
+        <v>259.89</v>
       </c>
       <c r="G110" t="n">
-        <v>79.86</v>
+        <v>257.39</v>
       </c>
       <c r="H110" t="n">
-        <v>10.17</v>
+        <v>23.15</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>[835.5, 962.55, 854.68]</t>
+          <t>[832.39, 876.02, 840.78]</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>[799.44, 776.04, 871.68]</t>
+          <t>[1052.23, 1181.78, 1087.37]</t>
         </is>
       </c>
     </row>
@@ -5502,12 +5502,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5521,22 +5521,22 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>199.96</v>
+        <v>189.45</v>
       </c>
       <c r="G111" t="n">
-        <v>165</v>
+        <v>188.75</v>
       </c>
       <c r="H111" t="n">
-        <v>18.93</v>
+        <v>18.34</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>[942.61, 845.8, 1237.22]</t>
+          <t>[980.0, 888.64, 676.84]</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>[776.04, 871.68, 934.66]</t>
+          <t>[1181.78, 1087.37, 842.58]</t>
         </is>
       </c>
     </row>
@@ -5548,17 +5548,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>(1, 1, 3)</t>
+          <t>(0, 1, 2)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -5567,22 +5567,22 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>274.12</v>
+        <v>112.42</v>
       </c>
       <c r="G112" t="n">
-        <v>249.74</v>
+        <v>109.45</v>
       </c>
       <c r="H112" t="n">
-        <v>54.16</v>
+        <v>31.35</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>[392.82, 254.83, 62.1]</t>
+          <t>[449.69, 347.49, 571.13]</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>[767.11, 529.05, 162.8]</t>
+          <t>[332.33, 272.7, 434.95]</t>
         </is>
       </c>
     </row>
@@ -5594,17 +5594,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>(0, 1, 3)</t>
+          <t>(3, 1, 0)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -5613,22 +5613,22 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>49.44</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="G113" t="n">
-        <v>45.34</v>
+        <v>68.67</v>
       </c>
       <c r="H113" t="n">
-        <v>25.21</v>
+        <v>15.2</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>[473.16, 100.39, 48.57]</t>
+          <t>[291.44, 504.17, 635.65]</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>[529.05, 162.8, 66.3]</t>
+          <t>[272.7, 434.95, 517.61]</t>
         </is>
       </c>
     </row>
@@ -5640,17 +5640,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>(0, 1, 3)</t>
+          <t>(3, 1, 0)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -5659,22 +5659,22 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>38.08</v>
+        <v>128.34</v>
       </c>
       <c r="G114" t="n">
-        <v>34.49</v>
+        <v>114.23</v>
       </c>
       <c r="H114" t="n">
-        <v>27.41</v>
+        <v>22.43</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>[107.4, 50.22, 101.59]</t>
+          <t>[484.55, 619.41, 719.47]</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>[162.8, 66.3, 133.58]</t>
+          <t>[434.95, 517.61, 528.19]</t>
         </is>
       </c>
     </row>
@@ -5686,17 +5686,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(3, 1, 0)</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -5705,22 +5705,22 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>8.17</v>
+        <v>183.2</v>
       </c>
       <c r="G115" t="n">
-        <v>6.74</v>
+        <v>164.03</v>
       </c>
       <c r="H115" t="n">
-        <v>4.93</v>
+        <v>25.09</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>[65.38, 121.36, 173.44]</t>
+          <t>[581.67, 692.28, 565.63]</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>[66.3, 133.58, 166.34]</t>
+          <t>[517.61, 528.19, 829.56]</t>
         </is>
       </c>
     </row>
@@ -5732,17 +5732,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(3, 1, 0)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -5751,22 +5751,22 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>12.05</v>
+        <v>215.15</v>
       </c>
       <c r="G116" t="n">
-        <v>11.71</v>
+        <v>202.34</v>
       </c>
       <c r="H116" t="n">
-        <v>7.42</v>
+        <v>30.95</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>[122.71, 175.06, 159.03]</t>
+          <t>[643.22, 535.54, 357.78]</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>[133.58, 166.34, 174.56]</t>
+          <t>[528.19, 829.56, 555.74]</t>
         </is>
       </c>
     </row>
@@ -5778,17 +5778,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>(1, 1, 1)</t>
+          <t>(3, 1, 0)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -5797,22 +5797,22 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>61.72</v>
+        <v>258.48</v>
       </c>
       <c r="G117" t="n">
-        <v>43.79</v>
+        <v>238</v>
       </c>
       <c r="H117" t="n">
-        <v>15.73</v>
+        <v>48.6</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>[183.99, 165.92, 437.41]</t>
+          <t>[465.31, 323.43, 77.98]</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>[166.34, 174.56, 332.33]</t>
+          <t>[829.56, 555.74, 195.42]</t>
         </is>
       </c>
     </row>
@@ -5824,12 +5824,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5839,26 +5839,26 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>60.26</v>
+        <v>69.2</v>
       </c>
       <c r="G118" t="n">
-        <v>54.09</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="H118" t="n">
-        <v>19.36</v>
+        <v>32.08</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>[154.35, 417.4, 329.69]</t>
+          <t>[472.1, 117.16, 50.54]</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>[174.56, 332.33, 272.7]</t>
+          <t>[555.74, 195.42, 85.87]</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5885,26 +5885,26 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>112.42</v>
+        <v>44.2</v>
       </c>
       <c r="G119" t="n">
-        <v>109.45</v>
+        <v>39.39</v>
       </c>
       <c r="H119" t="n">
-        <v>31.35</v>
+        <v>29.39</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>[449.69, 347.49, 571.13]</t>
+          <t>[128.67, 53.75, 96.93]</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>[332.33, 272.7, 434.95]</t>
+          <t>[195.42, 85.87, 116.23]</t>
         </is>
       </c>
     </row>
@@ -5916,17 +5916,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>(3, 1, 0)</t>
+          <t>(0, 1, 2)</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -5935,22 +5935,22 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>79.73999999999999</v>
+        <v>14.24</v>
       </c>
       <c r="G120" t="n">
-        <v>68.67</v>
+        <v>14.23</v>
       </c>
       <c r="H120" t="n">
-        <v>15.2</v>
+        <v>12.01</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>[291.44, 504.17, 635.65]</t>
+          <t>[71.31, 129.64, 180.38]</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>[272.7, 434.95, 517.61]</t>
+          <t>[85.87, 116.23, 195.09]</t>
         </is>
       </c>
     </row>
@@ -5962,17 +5962,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>(3, 1, 0)</t>
+          <t>(0, 1, 2)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -5981,22 +5981,22 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>128.34</v>
+        <v>18.06</v>
       </c>
       <c r="G121" t="n">
-        <v>114.23</v>
+        <v>12.76</v>
       </c>
       <c r="H121" t="n">
-        <v>22.43</v>
+        <v>10.16</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>[484.55, 619.41, 719.47]</t>
+          <t>[147.07, 198.88, 187.08]</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>[434.95, 517.61, 528.19]</t>
+          <t>[116.23, 195.09, 183.42]</t>
         </is>
       </c>
     </row>
@@ -6008,17 +6008,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 1, 3)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6027,22 +6027,22 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>34.07</v>
+        <v>4.81</v>
       </c>
       <c r="G122" t="n">
-        <v>23.33</v>
+        <v>4.03</v>
       </c>
       <c r="H122" t="n">
-        <v>136</v>
+        <v>51.79</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>[6.14, 10.4, 13.17]</t>
+          <t>[3.04, 1.44, 6.02]</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>[3.9, 68.6, 3.6]</t>
+          <t>[4.4, 4.6, 13.6]</t>
         </is>
       </c>
     </row>
@@ -6054,17 +6054,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 1, 3)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6073,22 +6073,22 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>34.66</v>
+        <v>4.31</v>
       </c>
       <c r="G123" t="n">
-        <v>22.61</v>
+        <v>4.13</v>
       </c>
       <c r="H123" t="n">
-        <v>105.01</v>
+        <v>50.3</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>[9.1, 11.52, 4.58]</t>
+          <t>[1.63, 7.78, 4.69]</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>[68.6, 3.6, 5.0]</t>
+          <t>[4.6, 13.6, 8.3]</t>
         </is>
       </c>
     </row>
@@ -6100,17 +6100,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>(0, 0, 3)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -6119,22 +6119,22 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>23.1</v>
+        <v>3.83</v>
       </c>
       <c r="G124" t="n">
-        <v>16.77</v>
+        <v>3.26</v>
       </c>
       <c r="H124" t="n">
-        <v>400.79</v>
+        <v>32.16</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>[15.42, 4.72, 42.62]</t>
+          <t>[8.15, 4.56, 4.61]</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>[3.6, 5.0, 4.4]</t>
+          <t>[13.6, 8.3, 5.2]</t>
         </is>
       </c>
     </row>
@@ -6146,17 +6146,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>(1, 1, 4)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -6165,22 +6165,22 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>13.96</v>
+        <v>2</v>
       </c>
       <c r="G125" t="n">
-        <v>9.380000000000001</v>
+        <v>1.52</v>
       </c>
       <c r="H125" t="n">
-        <v>221.92</v>
+        <v>24.74</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>[7.12, 28.39, 4.63]</t>
+          <t>[5.04, 5.08, 2.42]</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>[5.0, 4.4, 2.6]</t>
+          <t>[8.3, 5.2, 3.6]</t>
         </is>
       </c>
     </row>
@@ -6192,17 +6192,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>(0, 0, 3)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -6211,22 +6211,22 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>16.81</v>
+        <v>14.63</v>
       </c>
       <c r="G126" t="n">
-        <v>13.6</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="H126" t="n">
-        <v>360.88</v>
+        <v>22.77</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>[31.7, 6.94, 12.25]</t>
+          <t>[5.46, 2.6, 45.77]</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>[4.4, 2.6, 3.1]</t>
+          <t>[5.2, 3.6, 71.1]</t>
         </is>
       </c>
     </row>
@@ -6238,17 +6238,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>(2, 1, 1)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -6257,22 +6257,22 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>5.64</v>
+        <v>14.81</v>
       </c>
       <c r="G127" t="n">
-        <v>5.47</v>
+        <v>9.31</v>
       </c>
       <c r="H127" t="n">
-        <v>177.66</v>
+        <v>33.2</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>[10.03, 7.65, 8.81]</t>
+          <t>[2.59, 45.51, 2.39]</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>[2.6, 3.1, 4.4]</t>
+          <t>[3.6, 71.1, 3.7]</t>
         </is>
       </c>
     </row>
@@ -6284,17 +6284,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>(1, 1, 4)</t>
+          <t>(2, 1, 1)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -6303,22 +6303,22 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>3.73</v>
+        <v>12.15</v>
       </c>
       <c r="G128" t="n">
-        <v>2.56</v>
+        <v>7.49</v>
       </c>
       <c r="H128" t="n">
-        <v>78.29000000000001</v>
+        <v>21.89</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>[9.5, 3.72, 4.0]</t>
+          <t>[50.07, 2.9, 3.77]</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>[3.1, 4.4, 4.6]</t>
+          <t>[71.1, 3.7, 4.4]</t>
         </is>
       </c>
     </row>
@@ -6330,17 +6330,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>(1, 1, 3)</t>
+          <t>(2, 1, 1)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -6349,22 +6349,22 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>4.81</v>
+        <v>0.43</v>
       </c>
       <c r="G129" t="n">
-        <v>4.03</v>
+        <v>0.36</v>
       </c>
       <c r="H129" t="n">
-        <v>51.79</v>
+        <v>10.19</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>[3.04, 1.44, 6.02]</t>
+          <t>[3.08, 4.35, 3.61]</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>[4.4, 4.6, 13.6]</t>
+          <t>[3.7, 4.4, 3.2]</t>
         </is>
       </c>
     </row>
@@ -6376,17 +6376,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>(1, 1, 3)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -6395,22 +6395,22 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>4.31</v>
+        <v>0.72</v>
       </c>
       <c r="G130" t="n">
-        <v>4.13</v>
+        <v>0.6</v>
       </c>
       <c r="H130" t="n">
-        <v>50.3</v>
+        <v>17.64</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>[1.63, 7.78, 4.69]</t>
+          <t>[3.75, 3.3, 1.95]</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>[4.6, 13.6, 8.3]</t>
+          <t>[4.4, 3.2, 3.0]</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6441,22 +6441,22 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>3.83</v>
+        <v>0.76</v>
       </c>
       <c r="G131" t="n">
-        <v>3.26</v>
+        <v>0.67</v>
       </c>
       <c r="H131" t="n">
-        <v>32.16</v>
+        <v>21.61</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>[8.15, 4.56, 4.61]</t>
+          <t>[3.36, 1.99, 2.37]</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>[13.6, 8.3, 5.2]</t>
+          <t>[3.2, 3.0, 3.2]</t>
         </is>
       </c>
     </row>
@@ -6468,12 +6468,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6493,11 +6493,11 @@
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>2.734941534278958e+17</v>
+        <v>2.63031067106364e+18</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -6514,17 +6514,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(2, 0, 1)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -6539,11 +6539,11 @@
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>1.849181381654063e+17</v>
+        <v>2.141112405272927e+17</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -6560,17 +6560,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(2, 0, 1)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -6585,11 +6585,11 @@
         <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>1.556109516447669e+17</v>
+        <v>1.622776619905538e+17</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, -0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -6606,17 +6606,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(2, 0, 1)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -6631,11 +6631,11 @@
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>1.592912453716573e+17</v>
+        <v>1.378816642608752e+17</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, -0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -6652,17 +6652,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(2, 0, 1)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -6677,7 +6677,7 @@
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>2.340905323295787e+17</v>
+        <v>1.143292179451066e+17</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
@@ -6698,17 +6698,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(2, 0, 1)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -6723,11 +6723,11 @@
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>6.465049474320968e+17</v>
+        <v>9.293759120078875e+16</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, 0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -6744,12 +6744,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6769,11 +6769,11 @@
         <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>1.281313938479552e+18</v>
+        <v>7.430583208405118e+16</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, -0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -6790,17 +6790,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(2, 0, 1)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -6815,11 +6815,11 @@
         <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>2.63031067106364e+18</v>
+        <v>5.872393276001787e+16</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, -0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6861,7 +6861,7 @@
         <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>2.141112405272927e+17</v>
+        <v>4.587677514684841e+16</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6907,7 +6907,7 @@
         <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>1.622776619905538e+17</v>
+        <v>3.560333238678772e+16</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
@@ -6928,12 +6928,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -6943,26 +6943,26 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>83.40000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="G142" t="n">
-        <v>57.37</v>
+        <v>1.02</v>
       </c>
       <c r="H142" t="n">
-        <v>34.5</v>
+        <v>2.53</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>[66.73, 66.73, 66.73]</t>
+          <t>[22.61, 55.97, 50.16]</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>[76.1, 209.5, 86.7]</t>
+          <t>[23.4, 57.0, 51.4]</t>
         </is>
       </c>
     </row>
@@ -6974,12 +6974,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -6989,26 +6989,26 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>89.31999999999999</v>
+        <v>45.3</v>
       </c>
       <c r="G143" t="n">
-        <v>73.09</v>
+        <v>26.9</v>
       </c>
       <c r="H143" t="n">
-        <v>45.52</v>
+        <v>33.61</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>[67.17, 67.17, 67.17]</t>
+          <t>[55.97, 50.16, 159.64]</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>[209.5, 86.7, 124.6]</t>
+          <t>[57.0, 51.4, 81.2]</t>
         </is>
       </c>
     </row>
@@ -7020,12 +7020,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -7035,26 +7035,26 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>79.59</v>
+        <v>45.36</v>
       </c>
       <c r="G144" t="n">
-        <v>65.16</v>
+        <v>28</v>
       </c>
       <c r="H144" t="n">
-        <v>41.76</v>
+        <v>33.95</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>[70.91, 70.91, 70.91]</t>
+          <t>[50.16, 159.64, 156.41]</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>[86.7, 124.6, 196.9]</t>
+          <t>[51.4, 81.2, 152.1]</t>
         </is>
       </c>
     </row>
@@ -7066,41 +7066,41 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>81.39</v>
+        <v>45.36</v>
       </c>
       <c r="G145" t="n">
-        <v>73.01000000000001</v>
+        <v>27.65</v>
       </c>
       <c r="H145" t="n">
-        <v>94.31999999999999</v>
+        <v>33.23</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>[75.94, 73.05, 72.22]</t>
+          <t>[159.64, 156.41, 76.1]</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>[124.6, 196.9, 25.7]</t>
+          <t>[81.2, 152.1, 76.3]</t>
         </is>
       </c>
     </row>
@@ -7112,41 +7112,41 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>73.11</v>
+        <v>79.83</v>
       </c>
       <c r="G146" t="n">
-        <v>65.48</v>
+        <v>47.57</v>
       </c>
       <c r="H146" t="n">
-        <v>113.88</v>
+        <v>65.64</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>[86.58, 77.61, 75.1]</t>
+          <t>[156.41, 76.1, 209.5]</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>[196.9, 25.7, 40.9]</t>
+          <t>[152.1, 76.3, 71.3]</t>
         </is>
       </c>
     </row>
@@ -7158,17 +7158,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -7177,22 +7177,22 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>22.81</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="G147" t="n">
-        <v>14.48</v>
+        <v>48.87</v>
       </c>
       <c r="H147" t="n">
-        <v>37.76</v>
+        <v>67.58</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>[26.66, 80.27, 26.5]</t>
+          <t>[76.1, 209.5, 86.7]</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>[25.7, 40.9, 23.4]</t>
+          <t>[76.3, 71.3, 94.9]</t>
         </is>
       </c>
     </row>
@@ -7204,17 +7204,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -7223,22 +7223,22 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>24.51</v>
+        <v>80.23</v>
       </c>
       <c r="G148" t="n">
-        <v>17.7</v>
+        <v>52.8</v>
       </c>
       <c r="H148" t="n">
-        <v>43.18</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>[82.38, 26.47, 65.54]</t>
+          <t>[209.5, 86.7, 124.6]</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>[40.9, 23.4, 57.0]</t>
+          <t>[71.3, 94.9, 112.6]</t>
         </is>
       </c>
     </row>
@@ -7250,12 +7250,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7269,22 +7269,22 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1.04</v>
+        <v>29.79</v>
       </c>
       <c r="G149" t="n">
-        <v>1.02</v>
+        <v>23.23</v>
       </c>
       <c r="H149" t="n">
-        <v>2.53</v>
+        <v>17.63</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>[22.61, 55.97, 50.16]</t>
+          <t>[86.7, 124.6, 196.9]</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>[23.4, 57.0, 51.4]</t>
+          <t>[94.9, 112.6, 147.4]</t>
         </is>
       </c>
     </row>
@@ -7296,12 +7296,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7315,22 +7315,22 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>45.3</v>
+        <v>29.54</v>
       </c>
       <c r="G150" t="n">
-        <v>26.9</v>
+        <v>22.1</v>
       </c>
       <c r="H150" t="n">
-        <v>33.61</v>
+        <v>19.99</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>[55.97, 50.16, 159.64]</t>
+          <t>[124.6, 196.9, 25.7]</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>[57.0, 51.4, 81.2]</t>
+          <t>[112.6, 147.4, 30.5]</t>
         </is>
       </c>
     </row>
@@ -7342,12 +7342,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7361,22 +7361,22 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>45.36</v>
+        <v>30.44</v>
       </c>
       <c r="G151" t="n">
-        <v>28</v>
+        <v>23.93</v>
       </c>
       <c r="H151" t="n">
-        <v>33.95</v>
+        <v>41.37</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>[50.16, 159.64, 156.41]</t>
+          <t>[196.9, 25.7, 40.9]</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>[51.4, 81.2, 152.1]</t>
+          <t>[147.4, 30.5, 23.4]</t>
         </is>
       </c>
     </row>
@@ -7388,41 +7388,41 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>196.96</v>
+        <v>35.33</v>
       </c>
       <c r="G152" t="n">
-        <v>129.98</v>
+        <v>30.09</v>
       </c>
       <c r="H152" t="n">
-        <v>34.32</v>
+        <v>13.74</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>[162.52, 161.97, 161.43]</t>
+          <t>[237.66, 229.94, 306.92]</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>[129.91, 180.21, 500.52]</t>
+          <t>[189.78, 234.52, 269.1]</t>
         </is>
       </c>
     </row>
@@ -7434,41 +7434,41 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>203.99</v>
+        <v>216.58</v>
       </c>
       <c r="G153" t="n">
-        <v>140.02</v>
+        <v>145.47</v>
       </c>
       <c r="H153" t="n">
-        <v>35.84</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>[151.21, 150.83, 150.45]</t>
+          <t>[201.29, 299.91, 594.48]</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>[180.21, 500.52, 191.82]</t>
+          <t>[234.52, 269.1, 222.1]</t>
         </is>
       </c>
     </row>
@@ -7480,41 +7480,41 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>225.52</v>
+        <v>425.56</v>
       </c>
       <c r="G154" t="n">
-        <v>167.37</v>
+        <v>355</v>
       </c>
       <c r="H154" t="n">
-        <v>47.6</v>
+        <v>183.61</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>[119.79, 119.79, 119.79]</t>
+          <t>[329.28, 592.53, 809.8]</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>[500.52, 191.82, 169.13]</t>
+          <t>[269.1, 222.1, 175.4]</t>
         </is>
       </c>
     </row>
@@ -7526,41 +7526,41 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>231.14</v>
+        <v>737.0700000000001</v>
       </c>
       <c r="G155" t="n">
-        <v>147.33</v>
+        <v>668.33</v>
       </c>
       <c r="H155" t="n">
-        <v>30.42</v>
+        <v>438.58</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>[202.42, 201.63, 200.83]</t>
+          <t>[527.22, 810.93, 1194.76]</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>[191.82, 169.13, 599.72]</t>
+          <t>[222.1, 175.4, 130.43]</t>
         </is>
       </c>
     </row>
@@ -7572,41 +7572,41 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>232.98</v>
+        <v>733.4400000000001</v>
       </c>
       <c r="G156" t="n">
-        <v>150.91</v>
+        <v>670.22</v>
       </c>
       <c r="H156" t="n">
-        <v>32.2</v>
+        <v>483.75</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>[198.54, 197.82, 197.11]</t>
+          <t>[428.47, 958.33, 1067.98]</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>[169.13, 599.72, 175.68]</t>
+          <t>[175.4, 130.43, 138.3]</t>
         </is>
       </c>
     </row>
@@ -7618,17 +7618,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -7637,22 +7637,22 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>498.23</v>
+        <v>423.35</v>
       </c>
       <c r="G157" t="n">
-        <v>350.57</v>
+        <v>314.67</v>
       </c>
       <c r="H157" t="n">
-        <v>83.66</v>
+        <v>170.96</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>[1447.63, 227.69, 341.56]</t>
+          <t>[176.97, 329.35, 914.75]</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>[599.72, 175.68, 189.78]</t>
+          <t>[130.43, 138.3, 208.34]</t>
         </is>
       </c>
     </row>
@@ -7664,17 +7664,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -7683,22 +7683,22 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>77.06999999999999</v>
+        <v>328.3</v>
       </c>
       <c r="G158" t="n">
-        <v>61.23</v>
+        <v>260.69</v>
       </c>
       <c r="H158" t="n">
-        <v>30.31</v>
+        <v>138.9</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>[171.27, 308.83, 294.76]</t>
+          <t>[235.0, 749.92, 309.4]</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>[175.68, 189.78, 234.52]</t>
+          <t>[138.3, 208.34, 165.61]</t>
         </is>
       </c>
     </row>
@@ -7710,41 +7710,41 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>35.33</v>
+        <v>200.73</v>
       </c>
       <c r="G159" t="n">
-        <v>30.09</v>
+        <v>161.36</v>
       </c>
       <c r="H159" t="n">
-        <v>13.74</v>
+        <v>83.08</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>[237.66, 229.94, 306.92]</t>
+          <t>[538.38, 249.49, 244.78]</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>[189.78, 234.52, 269.1]</t>
+          <t>[208.34, 165.61, 174.63]</t>
         </is>
       </c>
     </row>
@@ -7756,17 +7756,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -7775,22 +7775,22 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>216.58</v>
+        <v>234.49</v>
       </c>
       <c r="G160" t="n">
-        <v>145.47</v>
+        <v>176.53</v>
       </c>
       <c r="H160" t="n">
-        <v>64.43000000000001</v>
+        <v>48.95</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>[201.29, 299.91, 594.48]</t>
+          <t>[134.14, 66.84, 200.04]</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>[234.52, 269.1, 222.1]</t>
+          <t>[165.61, 174.63, 590.36]</t>
         </is>
       </c>
     </row>
@@ -7802,17 +7802,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -7821,22 +7821,22 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>425.56</v>
+        <v>219.84</v>
       </c>
       <c r="G161" t="n">
-        <v>355</v>
+        <v>181.8</v>
       </c>
       <c r="H161" t="n">
-        <v>183.61</v>
+        <v>54.27</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>[329.28, 592.53, 809.8]</t>
+          <t>[79.1, 233.76, 102.22]</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>[269.1, 222.1, 175.4]</t>
+          <t>[174.63, 590.36, 195.49]</t>
         </is>
       </c>
     </row>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -7863,26 +7863,26 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>0.87</v>
+        <v>0.8</v>
       </c>
       <c r="G162" t="n">
-        <v>0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H162" t="n">
-        <v>37.67</v>
+        <v>9.277060316320865e+20</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0]</t>
+          <t>[0.06, 0.27, 0.01]</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>[2.2, 1.9, 0.9]</t>
+          <t>[0.4, 1.6, 0.0]</t>
         </is>
       </c>
     </row>
@@ -7894,12 +7894,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -7909,26 +7909,26 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="G163" t="n">
-        <v>0.67</v>
+        <v>0.47</v>
       </c>
       <c r="H163" t="n">
-        <v>7.870602934171938e+22</v>
+        <v>8.314697339828446e+21</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0]</t>
+          <t>[0.3, 0.01, 0.09]</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>[1.9, 0.9, 0.0]</t>
+          <t>[1.6, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -7940,12 +7940,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -7955,26 +7955,26 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>0.58</v>
+        <v>1.65</v>
       </c>
       <c r="G164" t="n">
-        <v>0.4</v>
+        <v>0.99</v>
       </c>
       <c r="H164" t="n">
-        <v>7.870602934171938e+22</v>
+        <v>9.225099622862309e+21</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0]</t>
+          <t>[0.01, 0.1, 0.74]</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>[0.9, 0.0, 1.1]</t>
+          <t>[0.0, 0.0, 3.6]</t>
         </is>
       </c>
     </row>
@@ -7986,12 +7986,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -8001,26 +8001,26 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>0.82</v>
+        <v>2.15</v>
       </c>
       <c r="G165" t="n">
-        <v>0.7</v>
+        <v>1.72</v>
       </c>
       <c r="H165" t="n">
-        <v>1.574120586834388e+23</v>
+        <v>4.574425118600038e+21</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0]</t>
+          <t>[0.06, 0.42, 0.27]</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>[0.0, 1.1, 0.0]</t>
+          <t>[0.0, 3.6, 2.2]</t>
         </is>
       </c>
     </row>
@@ -8032,12 +8032,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -8047,26 +8047,26 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>1.09</v>
+        <v>2.55</v>
       </c>
       <c r="G166" t="n">
-        <v>0.9</v>
+        <v>2.47</v>
       </c>
       <c r="H166" t="n">
-        <v>7.870602934171938e+22</v>
+        <v>93.7</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0]</t>
+          <t>[0.23, 0.14, 0.13]</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>[1.1, 0.0, 2.6]</t>
+          <t>[3.6, 2.2, 2.1]</t>
         </is>
       </c>
     </row>
@@ -8078,17 +8078,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -8097,22 +8097,22 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>3.09</v>
+        <v>1.73</v>
       </c>
       <c r="G167" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="H167" t="n">
-        <v>4.215356343329722e+23</v>
+        <v>93.09</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>[5.36, 2.53, 0.34]</t>
+          <t>[0.17, 0.14, 0.07]</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>[0.0, 2.6, 0.4]</t>
+          <t>[2.2, 2.1, 1.1]</t>
         </is>
       </c>
     </row>
@@ -8124,12 +8124,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8143,22 +8143,22 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>1.54</v>
+        <v>1.26</v>
       </c>
       <c r="G168" t="n">
-        <v>1.32</v>
+        <v>0.99</v>
       </c>
       <c r="H168" t="n">
-        <v>86.73999999999999</v>
+        <v>7.189352364201494e+16</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>[0.35, 0.05, 0.23]</t>
+          <t>[0.16, 0.08, -0.0]</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>[2.6, 0.4, 1.6]</t>
+          <t>[2.1, 1.1, 0.0]</t>
         </is>
       </c>
     </row>
@@ -8170,12 +8170,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -8189,22 +8189,22 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G169" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="H169" t="n">
-        <v>9.277060316320865e+20</v>
+        <v>7.101504649314144e+16</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>[0.06, 0.27, 0.01]</t>
+          <t>[0.09, -0.0, 0.11]</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>[0.4, 1.6, 0.0]</t>
+          <t>[1.1, 0.0, 1.3]</t>
         </is>
       </c>
     </row>
@@ -8216,12 +8216,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -8235,22 +8235,22 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>0.75</v>
+        <v>1.44</v>
       </c>
       <c r="G170" t="n">
-        <v>0.47</v>
+        <v>1.13</v>
       </c>
       <c r="H170" t="n">
-        <v>8.314697339828446e+21</v>
+        <v>7.007914867959542e+16</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>[0.3, 0.01, 0.09]</t>
+          <t>[-0.0, 0.12, -0.0]</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>[1.6, 0.0, 0.0]</t>
+          <t>[0.0, 1.3, 2.2]</t>
         </is>
       </c>
     </row>
@@ -8262,12 +8262,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -8281,22 +8281,22 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="G171" t="n">
-        <v>0.99</v>
+        <v>1.88</v>
       </c>
       <c r="H171" t="n">
-        <v>9.225099622862309e+21</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>[0.01, 0.1, 0.74]</t>
+          <t>[0.13, -0.0, 0.31]</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 3.6]</t>
+          <t>[1.3, 2.2, 2.6]</t>
         </is>
       </c>
     </row>
@@ -8308,17 +8308,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -8327,22 +8327,22 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>172.21</v>
+        <v>42.51</v>
       </c>
       <c r="G172" t="n">
-        <v>150.15</v>
+        <v>35.63</v>
       </c>
       <c r="H172" t="n">
-        <v>9.859999999999999</v>
+        <v>2.08</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>[1409.05, 1602.51, 1418.2]</t>
+          <t>[1647.21, 1535.58, 1727.44]</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>[1638.33, 1414.67, 1451.52]</t>
+          <t>[1617.42, 1524.98, 1793.94]</t>
         </is>
       </c>
     </row>
@@ -8354,17 +8354,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -8373,22 +8373,22 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>230.79</v>
+        <v>96.05</v>
       </c>
       <c r="G173" t="n">
-        <v>157.93</v>
+        <v>77.72</v>
       </c>
       <c r="H173" t="n">
-        <v>10.97</v>
+        <v>4.45</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>[1810.35, 1500.22, 1866.79]</t>
+          <t>[1517.52, 1713.9, 1881.36]</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>[1414.67, 1451.52, 1837.4]</t>
+          <t>[1524.98, 1793.94, 1735.7]</t>
         </is>
       </c>
     </row>
@@ -8400,17 +8400,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -8419,22 +8419,22 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>149.07</v>
+        <v>285.59</v>
       </c>
       <c r="G174" t="n">
-        <v>134.01</v>
+        <v>229.93</v>
       </c>
       <c r="H174" t="n">
-        <v>8.44</v>
+        <v>13.6</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>[1233.32, 1712.61, 1743.26]</t>
+          <t>[1719.38, 1885.4, 2127.69]</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>[1451.52, 1837.4, 1684.2]</t>
+          <t>[1793.94, 1735.7, 1662.16]</t>
         </is>
       </c>
     </row>
@@ -8446,17 +8446,17 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -8465,22 +8465,22 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>107.18</v>
+        <v>418.14</v>
       </c>
       <c r="G175" t="n">
-        <v>98.73</v>
+        <v>395.16</v>
       </c>
       <c r="H175" t="n">
-        <v>5.8</v>
+        <v>27.01</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>[1925.64, 1838.46, 1509.49]</t>
+          <t>[1938.05, 2166.31, 1706.01]</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>[1837.4, 1684.2, 1563.17]</t>
+          <t>[1735.7, 1662.16, 1227.05]</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -8511,22 +8511,22 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>278.62</v>
+        <v>327.43</v>
       </c>
       <c r="G176" t="n">
-        <v>210.39</v>
+        <v>313.36</v>
       </c>
       <c r="H176" t="n">
-        <v>13.56</v>
+        <v>22.37</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>[1796.58, 1510.75, 1987.24]</t>
+          <t>[2017.9, 1629.58, 1590.73]</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>[1684.2, 1563.17, 1520.87]</t>
+          <t>[1662.16, 1227.05, 1408.94]</t>
         </is>
       </c>
     </row>
@@ -8538,17 +8538,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -8557,22 +8557,22 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>339.49</v>
+        <v>272.66</v>
       </c>
       <c r="G177" t="n">
-        <v>313.84</v>
+        <v>226.9</v>
       </c>
       <c r="H177" t="n">
-        <v>20.07</v>
+        <v>14.37</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>[1428.69, 1956.14, 1989.19]</t>
+          <t>[1431.58, 1462.86, 1445.73]</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>[1563.17, 1520.87, 1617.42]</t>
+          <t>[1227.05, 1408.94, 1867.97]</t>
         </is>
       </c>
     </row>
@@ -8584,12 +8584,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -8603,22 +8603,22 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>385.25</v>
+        <v>322</v>
       </c>
       <c r="G178" t="n">
-        <v>366.32</v>
+        <v>261.78</v>
       </c>
       <c r="H178" t="n">
-        <v>23.58</v>
+        <v>15.31</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>[2026.07, 1997.19, 1738.98]</t>
+          <t>[1320.03, 1345.62, 1668.3]</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>[1520.87, 1617.42, 1524.98]</t>
+          <t>[1408.94, 1867.97, 1494.22]</t>
         </is>
       </c>
     </row>
@@ -8630,12 +8630,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -8649,22 +8649,22 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>42.51</v>
+        <v>307.5</v>
       </c>
       <c r="G179" t="n">
-        <v>35.63</v>
+        <v>275.25</v>
       </c>
       <c r="H179" t="n">
-        <v>2.08</v>
+        <v>16.31</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>[1647.21, 1535.58, 1727.44]</t>
+          <t>[1404.73, 1716.54, 1653.06]</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>[1617.42, 1524.98, 1793.94]</t>
+          <t>[1867.97, 1494.22, 1512.88]</t>
         </is>
       </c>
     </row>
@@ -8676,17 +8676,17 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -8695,22 +8695,22 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>96.05</v>
+        <v>426.35</v>
       </c>
       <c r="G180" t="n">
-        <v>77.72</v>
+        <v>374.06</v>
       </c>
       <c r="H180" t="n">
-        <v>4.45</v>
+        <v>24.75</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>[1517.52, 1713.9, 1881.36]</t>
+          <t>[2134.1, 1852.93, 1729.12]</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>[1524.98, 1793.94, 1735.7]</t>
+          <t>[1494.22, 1512.88, 1586.88]</t>
         </is>
       </c>
     </row>
@@ -8722,17 +8722,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(1, 0, 2)</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -8741,22 +8741,22 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>285.59</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="G181" t="n">
-        <v>229.93</v>
+        <v>59.33</v>
       </c>
       <c r="H181" t="n">
-        <v>13.6</v>
+        <v>3.87</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>[1719.38, 1885.4, 2127.69]</t>
+          <t>[1402.36, 1542.24, 1552.01]</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>[1793.94, 1735.7, 1662.16]</t>
+          <t>[1512.88, 1586.88, 1529.18]</t>
         </is>
       </c>
     </row>
@@ -8768,12 +8768,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -8787,22 +8787,22 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>754.83</v>
+        <v>303.66</v>
       </c>
       <c r="G182" t="n">
-        <v>729.0599999999999</v>
+        <v>273.53</v>
       </c>
       <c r="H182" t="n">
-        <v>45.06</v>
+        <v>20.74</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>[911.62, 753.21, 924.88]</t>
+          <t>[1349.24, 1219.14, 2036.98]</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>[1714.02, 1676.54, 1386.32]</t>
+          <t>[1183.77, 1023.24, 1577.77]</t>
         </is>
       </c>
     </row>
@@ -8814,12 +8814,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -8833,22 +8833,22 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>482.98</v>
+        <v>252.85</v>
       </c>
       <c r="G183" t="n">
-        <v>434.82</v>
+        <v>223.9</v>
       </c>
       <c r="H183" t="n">
-        <v>27.71</v>
+        <v>16.64</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>[976.06, 1199.92, 1079.76]</t>
+          <t>[1170.44, 1967.64, 1377.87]</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>[1676.54, 1386.32, 1497.36]</t>
+          <t>[1023.24, 1577.77, 1243.23]</t>
         </is>
       </c>
     </row>
@@ -8860,17 +8860,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(3, 0, 0)</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -8879,22 +8879,22 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>168.28</v>
+        <v>236.57</v>
       </c>
       <c r="G184" t="n">
-        <v>165.18</v>
+        <v>212.59</v>
       </c>
       <c r="H184" t="n">
-        <v>12.43</v>
+        <v>12.49</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>[1521.91, 1347.21, 1410.62]</t>
+          <t>[1856.58, 1309.27, 1727.18]</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>[1386.32, 1497.36, 1200.8]</t>
+          <t>[1577.77, 1243.23, 2020.1]</t>
         </is>
       </c>
     </row>
@@ -8906,17 +8906,17 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(3, 0, 0)</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -8925,22 +8925,22 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>427.79</v>
+        <v>227.22</v>
       </c>
       <c r="G185" t="n">
-        <v>352.75</v>
+        <v>170.94</v>
       </c>
       <c r="H185" t="n">
-        <v>21</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>[1297.63, 1364.93, 1235.15]</t>
+          <t>[1245.33, 1654.16, 1544.39]</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>[1497.36, 1200.8, 1929.55]</t>
+          <t>[1243.23, 2020.1, 1689.17]</t>
         </is>
       </c>
     </row>
@@ -8952,17 +8952,17 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(3, 0, 0)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -8971,22 +8971,22 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>399.6</v>
+        <v>247.6</v>
       </c>
       <c r="G186" t="n">
-        <v>332.49</v>
+        <v>226.74</v>
       </c>
       <c r="H186" t="n">
-        <v>19.84</v>
+        <v>12.17</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>[1435.62, 1290.28, 1931.05]</t>
+          <t>[1653.26, 1543.65, 1554.09]</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>[1200.8, 1929.55, 1807.66]</t>
+          <t>[2020.1, 1689.17, 1721.94]</t>
         </is>
       </c>
     </row>
@@ -8998,12 +8998,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -9017,22 +9017,22 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>417.41</v>
+        <v>180.08</v>
       </c>
       <c r="G187" t="n">
-        <v>284.2</v>
+        <v>142.39</v>
       </c>
       <c r="H187" t="n">
-        <v>15.5</v>
+        <v>8.42</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>[1213.03, 1880.41, 1247.1]</t>
+          <t>[1642.48, 1638.31, 1387.16]</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>[1929.55, 1807.66, 1183.77]</t>
+          <t>[1689.17, 1721.94, 1684.0]</t>
         </is>
       </c>
     </row>
@@ -9044,12 +9044,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -9063,22 +9063,22 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>302.74</v>
+        <v>268.4</v>
       </c>
       <c r="G188" t="n">
-        <v>297.57</v>
+        <v>238.49</v>
       </c>
       <c r="H188" t="n">
-        <v>23.05</v>
+        <v>13.48</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>[2164.32, 1406.69, 1336.37]</t>
+          <t>[1652.5, 1397.19, 1493.53]</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>[1807.66, 1183.77, 1023.24]</t>
+          <t>[1721.94, 1684.0, 1852.75]</t>
         </is>
       </c>
     </row>
@@ -9090,17 +9090,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(3, 0, 0)</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -9109,22 +9109,22 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>303.66</v>
+        <v>333.08</v>
       </c>
       <c r="G189" t="n">
-        <v>273.53</v>
+        <v>330</v>
       </c>
       <c r="H189" t="n">
-        <v>20.74</v>
+        <v>19.41</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>[1349.24, 1219.14, 2036.98]</t>
+          <t>[1414.78, 1509.54, 1213.51]</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>[1183.77, 1023.24, 1577.77]</t>
+          <t>[1684.0, 1852.75, 1591.07]</t>
         </is>
       </c>
     </row>
@@ -9136,17 +9136,17 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(3, 0, 0)</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -9155,22 +9155,22 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>252.85</v>
+        <v>425.83</v>
       </c>
       <c r="G190" t="n">
-        <v>223.9</v>
+        <v>397.56</v>
       </c>
       <c r="H190" t="n">
-        <v>16.64</v>
+        <v>25.54</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>[1170.44, 1967.64, 1377.87]</t>
+          <t>[1592.13, 1269.44, 2051.95]</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>[1023.24, 1577.77, 1243.23]</t>
+          <t>[1852.75, 1591.07, 1441.53]</t>
         </is>
       </c>
     </row>
@@ -9182,12 +9182,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -9201,22 +9201,22 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>236.57</v>
+        <v>633.99</v>
       </c>
       <c r="G191" t="n">
-        <v>212.59</v>
+        <v>588.17</v>
       </c>
       <c r="H191" t="n">
-        <v>12.49</v>
+        <v>31.2</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>[1856.58, 1309.27, 1727.18]</t>
+          <t>[1330.52, 2134.34, 1968.9]</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>[1577.77, 1243.23, 2020.1]</t>
+          <t>[1591.07, 1441.53, 2780.05]</t>
         </is>
       </c>
     </row>
@@ -9228,17 +9228,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 1, 2)</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -9247,22 +9247,22 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="G192" t="n">
-        <v>1.59</v>
+        <v>0.89</v>
       </c>
       <c r="H192" t="n">
-        <v>85.3</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>[0.13, 0.24, 0.37]</t>
+          <t>[1.53, 0.02, 0.06]</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>[0.7, 2.3, 2.5]</t>
+          <t>[2.2, 0.5, 1.6]</t>
         </is>
       </c>
     </row>
@@ -9274,17 +9274,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>(4, 1, 2)</t>
+          <t>(1, 1, 2)</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -9293,22 +9293,22 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>1.8</v>
+        <v>3.41</v>
       </c>
       <c r="G193" t="n">
-        <v>1.59</v>
+        <v>2.56</v>
       </c>
       <c r="H193" t="n">
-        <v>80.06999999999999</v>
+        <v>95.73</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>[0.05, 0.39, 0.3]</t>
+          <t>[0.03, 0.06, 0.22]</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>[2.3, 2.5, 0.7]</t>
+          <t>[0.5, 1.6, 5.9]</t>
         </is>
       </c>
     </row>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -9335,26 +9335,26 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F194" t="n">
-        <v>0.63</v>
+        <v>4.54</v>
       </c>
       <c r="G194" t="n">
-        <v>0.51</v>
+        <v>4.14</v>
       </c>
       <c r="H194" t="n">
-        <v>32.63</v>
+        <v>94.06</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>[1.51, 0.8, 0.57]</t>
+          <t>[0.1, 0.36, 0.32]</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>[2.5, 0.7, 1.0]</t>
+          <t>[1.6, 5.9, 5.7]</t>
         </is>
       </c>
     </row>
@@ -9366,12 +9366,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -9381,26 +9381,26 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F195" t="n">
-        <v>0.95</v>
+        <v>4.35</v>
       </c>
       <c r="G195" t="n">
-        <v>0.73</v>
+        <v>3.65</v>
       </c>
       <c r="H195" t="n">
-        <v>1.256363739971023e+23</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>[1.01, 0.71, 1.6]</t>
+          <t>[0.5, 0.44, 0.1]</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>[0.7, 1.0, 0.0]</t>
+          <t>[5.9, 5.7, 0.4]</t>
         </is>
       </c>
     </row>
@@ -9412,12 +9412,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -9427,26 +9427,26 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>2.19</v>
+        <v>2.99</v>
       </c>
       <c r="G196" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="H196" t="n">
-        <v>1.046043826071287e+23</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>[0.55, 1.33, 1.58]</t>
+          <t>[0.58, 0.13, 0.43]</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>[1.0, 0.0, 5.1]</t>
+          <t>[5.7, 0.4, 1.1]</t>
         </is>
       </c>
     </row>
@@ -9458,12 +9458,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -9473,26 +9473,26 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>2.05</v>
+        <v>0.76</v>
       </c>
       <c r="G197" t="n">
-        <v>1.62</v>
+        <v>0.65</v>
       </c>
       <c r="H197" t="n">
-        <v>1.311304863576344e+23</v>
+        <v>57.04</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>[1.67, 1.97, 2.13]</t>
+          <t>[0.17, 0.57, 0.62]</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>[0.0, 5.1, 2.2]</t>
+          <t>[0.4, 1.1, 1.8]</t>
         </is>
       </c>
     </row>
@@ -9504,12 +9504,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -9523,22 +9523,22 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="G198" t="n">
-        <v>2.34</v>
+        <v>0.59</v>
       </c>
       <c r="H198" t="n">
-        <v>89.42</v>
+        <v>51.82</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>[0.19, 0.57, 0.01]</t>
+          <t>[0.64, 0.69, 0.19]</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>[5.1, 2.2, 0.5]</t>
+          <t>[1.1, 1.8, 0.4]</t>
         </is>
       </c>
     </row>
@@ -9550,17 +9550,17 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>(1, 1, 2)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -9569,22 +9569,22 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>1.01</v>
+        <v>0.66</v>
       </c>
       <c r="G199" t="n">
-        <v>0.89</v>
+        <v>0.55</v>
       </c>
       <c r="H199" t="n">
-        <v>73.90000000000001</v>
+        <v>54.5</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>[1.53, 0.02, 0.06]</t>
+          <t>[0.75, 0.21, 0.3]</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>[2.2, 0.5, 1.6]</t>
+          <t>[1.8, 0.4, 0.7]</t>
         </is>
       </c>
     </row>
@@ -9596,17 +9596,17 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>(1, 1, 2)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -9615,22 +9615,22 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>3.41</v>
+        <v>0.26</v>
       </c>
       <c r="G200" t="n">
-        <v>2.56</v>
+        <v>0.24</v>
       </c>
       <c r="H200" t="n">
-        <v>95.73</v>
+        <v>63.91</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>[0.03, 0.06, 0.22]</t>
+          <t>[0.24, 0.34, -0.0]</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>[0.5, 1.6, 5.9]</t>
+          <t>[0.4, 0.7, 0.2]</t>
         </is>
       </c>
     </row>
@@ -9642,12 +9642,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -9661,22 +9661,22 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>4.54</v>
+        <v>0.36</v>
       </c>
       <c r="G201" t="n">
-        <v>4.14</v>
+        <v>0.34</v>
       </c>
       <c r="H201" t="n">
-        <v>94.06</v>
+        <v>60.56</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>[0.1, 0.36, 0.32]</t>
+          <t>[0.37, -0.0, 1.88]</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>[1.6, 5.9, 5.7]</t>
+          <t>[0.7, 0.2, 1.4]</t>
         </is>
       </c>
     </row>
